--- a/evaluation_forms/018_service_proposal_value_assessment--evaluation_forms.xlsx
+++ b/evaluation_forms/018_service_proposal_value_assessment--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -704,8 +704,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -733,12 +733,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'software_development'}</t>
+          <t>software_development</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Software Development'}</t>
+          <t>Software Development</t>
         </is>
       </c>
     </row>
@@ -767,12 +767,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'consulting'}</t>
+          <t>consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Consulting'}</t>
+          <t>Consulting</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'training'}</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Training'}</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'financial_savings'}</t>
+          <t>financial_savings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Financial Savings'}</t>
+          <t>Financial Savings</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'improved_efficiency'}</t>
+          <t>improved_efficiency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Improved Efficiency'}</t>
+          <t>Improved Efficiency</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'reduced_risk'}</t>
+          <t>reduced_risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Reduced Risk'}</t>
+          <t>Reduced Risk</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
